--- a/client/public/CCPL_Master_Import_Template.xlsx
+++ b/client/public/CCPL_Master_Import_Template.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Energy_Water_STP" sheetId="10" r:id="rId10"/>
     <sheet name="Energy_Air_Compressor" sheetId="11" r:id="rId11"/>
     <sheet name="Energy_Daily_Solar" sheetId="12" r:id="rId12"/>
-    <sheet name="README" sheetId="13" r:id="rId13"/>
+    <sheet name="KPI_Status" sheetId="13" r:id="rId13"/>
+    <sheet name="README" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -471,10 +472,10 @@
         <v>87.5</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-09-05T08:00</v>
+        <v>2026-09-08T08:00</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-09-05T16:00</v>
+        <v>2026-09-08T16:00</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -500,10 +501,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-09-05T09:00</v>
+        <v>2026-09-08T09:00</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-09-05T13:00</v>
+        <v>2026-09-08T13:00</v>
       </c>
       <c r="I3" t="str">
         <v>All done</v>
@@ -684,7 +685,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="B2">
         <v>320</v>
@@ -716,7 +717,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -755,7 +756,136 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:K3"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Month</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Plant/Section</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Machine/Equipment</v>
+      </c>
+      <c r="D1" t="str">
+        <v>PM Compliance %</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Breakdown Count</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Breakdown Hours</v>
+      </c>
+      <c r="G1" t="str">
+        <v>MTTR</v>
+      </c>
+      <c r="H1" t="str">
+        <v>MTBF</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Availability %</v>
+      </c>
+      <c r="J1" t="str">
+        <v>KPI Status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Remarks</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Herbi EC Packaging</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2">
+        <v>92.5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>12.5</v>
+      </c>
+      <c r="G2">
+        <v>4.2</v>
+      </c>
+      <c r="H2">
+        <v>235.8</v>
+      </c>
+      <c r="I2">
+        <v>98.2</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Good</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Auto calculated; manual override allowed</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09</v>
+      </c>
+      <c r="B3" t="str">
+        <v>EC INSEC Packaging</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Filling Machine #1</v>
+      </c>
+      <c r="D3">
+        <v>85</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>4.4</v>
+      </c>
+      <c r="H3">
+        <v>139.6</v>
+      </c>
+      <c r="I3">
+        <v>96.9</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Per-machine KPI</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D15"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -947,21 +1077,35 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>KPI_Status</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Monthly KPI per Section/Machine (11 cols)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Month, Plant/Section</v>
+      </c>
+      <c r="D14" t="str">
+        <v>KPI Status auto from thresholds if blank; values auto from PM/Breakdown if blank</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>README</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B15" t="str">
         <v>This index</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C15" t="str">
         <v>-</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D15" t="str">
         <v>Keep headers exactly as row 1 — aliases handle variants</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1124,10 +1268,10 @@
         <v>Herbi EC Packaging</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-09-05T08:00</v>
+        <v>2026-09-08T08:00</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-09-05T12:30</v>
+        <v>2026-09-08T12:30</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -1298,7 +1442,7 @@
         <v>Herbi EC Packaging</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="E2" t="str">
         <v>Preventive</v>
@@ -1330,7 +1474,7 @@
         <v>Herbi EC Packaging</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="E3" t="str">
         <v>Preventive</v>
@@ -1444,7 +1588,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="B2" t="str">
         <v>Utility Section</v>
@@ -1626,7 +1770,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-08</v>
       </c>
       <c r="B2">
         <v>4200</v>

--- a/client/public/CCPL_Master_Import_Template.xlsx
+++ b/client/public/CCPL_Master_Import_Template.xlsx
@@ -756,129 +756,1451 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:AA17"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Month</v>
+        <v>Sn</v>
       </c>
       <c r="B1" t="str">
-        <v>Plant/Section</v>
+        <v>Focus Pillar</v>
       </c>
       <c r="C1" t="str">
-        <v>Machine/Equipment</v>
+        <v>KPI / Metric</v>
       </c>
       <c r="D1" t="str">
-        <v>PM Compliance %</v>
+        <v>UoM</v>
       </c>
       <c r="E1" t="str">
-        <v>Breakdown Count</v>
+        <v>KPI Wt %</v>
       </c>
       <c r="F1" t="str">
-        <v>Breakdown Hours</v>
+        <v>Pillar Wt %</v>
       </c>
       <c r="G1" t="str">
-        <v>MTTR</v>
+        <v>Annual Target (Rating 3)</v>
       </c>
       <c r="H1" t="str">
-        <v>MTBF</v>
+        <v>Rating 4</v>
       </c>
       <c r="I1" t="str">
-        <v>Availability %</v>
+        <v>Rating 5</v>
       </c>
       <c r="J1" t="str">
-        <v>KPI Status</v>
+        <v>Parent Target</v>
       </c>
       <c r="K1" t="str">
-        <v>Remarks</v>
+        <v>Q1 Apr–Jun</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Q2 Jul–Sep</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Q3 Oct–Dec</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Q4 Jan–Mar</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Apr</v>
+      </c>
+      <c r="P1" t="str">
+        <v>May</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Jun</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Sep</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Jan</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Feb</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Mar</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>YTD Avg</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>2026-09</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Herbi EC Packaging</v>
+        <v>P – Productivity</v>
       </c>
       <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2">
-        <v>92.5</v>
+        <v>Asset / Equipment Availability – Plant</v>
+      </c>
+      <c r="D2" t="str">
+        <v>%</v>
       </c>
       <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>37</v>
+      </c>
+      <c r="G2" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="H2" t="str">
+        <v>&gt;=97</v>
+      </c>
+      <c r="I2" t="str">
+        <v>&gt;=99</v>
+      </c>
+      <c r="J2" t="str">
+        <v>&gt;=95% (Engg Head)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="L2" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="M2" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="N2" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>P – Productivity</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PM Schedule Adherence – Plant</v>
+      </c>
+      <c r="D3" t="str">
+        <v>%</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="H3" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="I3" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="J3" t="str">
+        <v>&gt;=90% (Engg Head)</v>
+      </c>
+      <c r="K3" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="L3" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="M3" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="N3" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>12.5</v>
-      </c>
-      <c r="G2">
-        <v>4.2</v>
-      </c>
-      <c r="H2">
-        <v>235.8</v>
-      </c>
-      <c r="I2">
-        <v>98.2</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Good</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Auto calculated; manual override allowed</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-09</v>
-      </c>
-      <c r="B3" t="str">
-        <v>EC INSEC Packaging</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Filling Machine #1</v>
-      </c>
-      <c r="D3">
-        <v>85</v>
-      </c>
-      <c r="E3">
+      <c r="B4" t="str">
+        <v>P – Productivity</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Breakdown Frequency Reduction (MTBF improvement)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>% improve</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="H4" t="str">
+        <v>&gt;=15</v>
+      </c>
+      <c r="I4" t="str">
+        <v>&gt;=20</v>
+      </c>
+      <c r="J4" t="str">
+        <v>&gt;=10% (Engg Head)</v>
+      </c>
+      <c r="K4" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="L4" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="M4" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="N4" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>P – Productivity</v>
+      </c>
+      <c r="C5" t="str">
+        <v>MTTR – Mean Time to Repair Reduction</v>
+      </c>
+      <c r="D5" t="str">
+        <v>% improve</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>4.4</v>
-      </c>
-      <c r="H3">
-        <v>139.6</v>
-      </c>
-      <c r="I3">
-        <v>96.9</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Warning</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Per-machine KPI</v>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="H5" t="str">
+        <v>&gt;=15</v>
+      </c>
+      <c r="I5" t="str">
+        <v>&gt;=20</v>
+      </c>
+      <c r="J5" t="str">
+        <v>&gt;=10% (Engg Head)</v>
+      </c>
+      <c r="K5" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="L5" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="M5" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="N5" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Q – Quality</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Equipment Calibration Compliance – Plant</v>
+      </c>
+      <c r="D6" t="str">
+        <v>%</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="H6" t="str">
+        <v>&gt;=99</v>
+      </c>
+      <c r="I6" t="str">
+        <v>100</v>
+      </c>
+      <c r="J6" t="str">
+        <v>&gt;=98% (Engg Head)</v>
+      </c>
+      <c r="K6" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="L6" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="M6" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="N6" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Q – Quality</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Audit/ Regulatory NC – Engineering – Plant</v>
+      </c>
+      <c r="D7" t="str">
+        <v>No. NCs</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>&lt;=1</v>
+      </c>
+      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <v>&lt;=2 consolidated</v>
+      </c>
+      <c r="K7" t="str">
+        <v>&lt;=1</v>
+      </c>
+      <c r="L7" t="str">
+        <v>&lt;=1</v>
+      </c>
+      <c r="M7" t="str">
+        <v>&lt;=1</v>
+      </c>
+      <c r="N7" t="str">
+        <v>&lt;=1</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>S – Safety &amp; Environment</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Zero LTI – Engineering / Maintenance – Plant</v>
+      </c>
+      <c r="D8" t="str">
+        <v>No. LTI</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>0</v>
+      </c>
+      <c r="J8" t="str">
+        <v>0 (Engg Head)</v>
+      </c>
+      <c r="K8" t="str">
+        <v>0</v>
+      </c>
+      <c r="L8" t="str">
+        <v>0</v>
+      </c>
+      <c r="M8" t="str">
+        <v>0</v>
+      </c>
+      <c r="N8" t="str">
+        <v>0</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>S – Safety &amp; Environment</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Near Miss Reporting – Production Team</v>
+      </c>
+      <c r="D9" t="str">
+        <v>No./Person/Mo</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="H9" t="str">
+        <v>&gt;=2.5</v>
+      </c>
+      <c r="I9" t="str">
+        <v>&gt;=3</v>
+      </c>
+      <c r="J9" t="str">
+        <v>&gt;=2 (HSE Head)</v>
+      </c>
+      <c r="K9" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="L9" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="M9" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="N9" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>S – Safety &amp; Environment</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LOTO / PTW Compliance – Plant</v>
+      </c>
+      <c r="D10" t="str">
+        <v>%</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="H10" t="str">
+        <v>&gt;=99</v>
+      </c>
+      <c r="I10" t="str">
+        <v>100</v>
+      </c>
+      <c r="J10" t="str">
+        <v>&gt;=98%</v>
+      </c>
+      <c r="K10" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="L10" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="M10" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="N10" t="str">
+        <v>&gt;=98</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>S – Safety &amp; Environment</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ETP / STP Efficiency – Plant</v>
+      </c>
+      <c r="D11" t="str">
+        <v>%</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>&gt;=80</v>
+      </c>
+      <c r="H11" t="str">
+        <v>&gt;=85</v>
+      </c>
+      <c r="I11" t="str">
+        <v>&gt;=90</v>
+      </c>
+      <c r="J11" t="str">
+        <v>&gt;=80% (Engg Head)</v>
+      </c>
+      <c r="K11" t="str">
+        <v>&gt;=80</v>
+      </c>
+      <c r="L11" t="str">
+        <v>&gt;=80</v>
+      </c>
+      <c r="M11" t="str">
+        <v>&gt;=80</v>
+      </c>
+      <c r="N11" t="str">
+        <v>&gt;=80</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>C – Cost &amp; OpEx</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Energy Cost Reduction – Plant</v>
+      </c>
+      <c r="D12" t="str">
+        <v>% vs LY</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+      <c r="G12" t="str">
+        <v>&gt;=5</v>
+      </c>
+      <c r="H12" t="str">
+        <v>&gt;=8</v>
+      </c>
+      <c r="I12" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="J12" t="str">
+        <v>&gt;=5% (Engg Head)</v>
+      </c>
+      <c r="K12" t="str">
+        <v>&gt;=5</v>
+      </c>
+      <c r="L12" t="str">
+        <v>&gt;=5</v>
+      </c>
+      <c r="M12" t="str">
+        <v>&gt;=5</v>
+      </c>
+      <c r="N12" t="str">
+        <v>&gt;=5</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>C – Cost &amp; OpEx</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Maintenance Cost vs Budget – Plant</v>
+      </c>
+      <c r="D13" t="str">
+        <v>%</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>&lt;=100</v>
+      </c>
+      <c r="H13" t="str">
+        <v>&lt;=98</v>
+      </c>
+      <c r="I13" t="str">
+        <v>&lt;=95</v>
+      </c>
+      <c r="J13" t="str">
+        <v>&lt;=100%</v>
+      </c>
+      <c r="K13" t="str">
+        <v>&lt;=100</v>
+      </c>
+      <c r="L13" t="str">
+        <v>&lt;=100</v>
+      </c>
+      <c r="M13" t="str">
+        <v>&lt;=100</v>
+      </c>
+      <c r="N13" t="str">
+        <v>&lt;=100</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>C – Cost &amp; OpEx</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Spare Parts Inventory Optimisation – Plant</v>
+      </c>
+      <c r="D14" t="str">
+        <v>% reduction</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="H14" t="str">
+        <v>&gt;=15</v>
+      </c>
+      <c r="I14" t="str">
+        <v>&gt;=20</v>
+      </c>
+      <c r="J14" t="str">
+        <v>&gt;=10%</v>
+      </c>
+      <c r="K14" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="L14" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="M14" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="N14" t="str">
+        <v>&gt;=10</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>D – Delivery / OTIF</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Engineering Clearance for Production – On Time</v>
+      </c>
+      <c r="D15" t="str">
+        <v>% requests</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="H15" t="str">
+        <v>&gt;=97</v>
+      </c>
+      <c r="I15" t="str">
+        <v>100</v>
+      </c>
+      <c r="J15" t="str">
+        <v>&gt;=95%</v>
+      </c>
+      <c r="K15" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="L15" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="M15" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="N15" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>M – Morale &amp; People</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Engg Team Training Mandays – Plant</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Mandays/Yr</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="H16" t="str">
+        <v>&gt;=3</v>
+      </c>
+      <c r="I16" t="str">
+        <v>&gt;=4</v>
+      </c>
+      <c r="J16" t="str">
+        <v>&gt;=2%</v>
+      </c>
+      <c r="K16" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="L16" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="M16" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="N16" t="str">
+        <v>&gt;=2</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>M – Morale &amp; People</v>
+      </c>
+      <c r="C17" t="str">
+        <v>5S – Engineering Areas – Plant</v>
+      </c>
+      <c r="D17" t="str">
+        <v>%</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>&gt;=75</v>
+      </c>
+      <c r="H17" t="str">
+        <v>&gt;=85</v>
+      </c>
+      <c r="I17" t="str">
+        <v>&gt;=95</v>
+      </c>
+      <c r="J17" t="str">
+        <v>&gt;=75%</v>
+      </c>
+      <c r="K17" t="str">
+        <v>&gt;=75</v>
+      </c>
+      <c r="L17" t="str">
+        <v>&gt;=75</v>
+      </c>
+      <c r="M17" t="str">
+        <v>&gt;=75</v>
+      </c>
+      <c r="N17" t="str">
+        <v>&gt;=75</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1080,13 +2402,13 @@
         <v>KPI_Status</v>
       </c>
       <c r="B14" t="str">
-        <v>Monthly KPI per Section/Machine (11 cols)</v>
+        <v>FY 2026-27 PQSCDM Goal Cascade — Plant Engg Manager (27 cols)</v>
       </c>
       <c r="C14" t="str">
-        <v>Month, Plant/Section</v>
+        <v>Sn, KPI / Metric</v>
       </c>
       <c r="D14" t="str">
-        <v>KPI Status auto from thresholds if blank; values auto from PM/Breakdown if blank</v>
+        <v>Q1-Q4 auto = Annual Target if blank; Apr-Mar editable; YTD Avg auto; Auto values from PM/Breakdown/Energy where applicable</v>
       </c>
     </row>
     <row r="15">
